--- a/artfynd/S 742-2025 artfynd.xlsx
+++ b/artfynd/S 742-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>130343069</v>
       </c>
       <c r="B3" t="n">
-        <v>96773</v>
+        <v>96776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 742-2025 artfynd.xlsx
+++ b/artfynd/S 742-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>130343069</v>
       </c>
       <c r="B3" t="n">
-        <v>96776</v>
+        <v>96777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 742-2025 artfynd.xlsx
+++ b/artfynd/S 742-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>130343069</v>
       </c>
       <c r="B3" t="n">
-        <v>96777</v>
+        <v>96782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
